--- a/config_Kim.xlsx
+++ b/config_Kim.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://smu-my.sharepoint.com/personal/keithtan_2022_accountancy_smu_edu_sg/Documents/Desktop/smu/subject/y4s2/capstone/ETL/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="29" documentId="11_AD4DB114E441178AC67DF4960696DC8E693EDF12" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{414A111B-84DE-4D1B-9641-FAB8AC7654CB}"/>
+  <xr:revisionPtr revIDLastSave="33" documentId="11_AD4DB114E441178AC67DF4960696DC8E693EDF12" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8239CBB6-9DBA-4364-B786-E6359BDA72CC}"/>
   <bookViews>
-    <workbookView xWindow="30750" yWindow="2580" windowWidth="21600" windowHeight="11265" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="paths" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
   <si>
     <t>raw_data</t>
   </si>
@@ -71,6 +71,12 @@
   </si>
   <si>
     <t>tenant_turnover</t>
+  </si>
+  <si>
+    <t>C:\Users\user\OneDrive - Singapore Management University\Desktop\smu\subject\y4s2\capstone\combined data</t>
+  </si>
+  <si>
+    <t>combined_data</t>
   </si>
 </sst>
 </file>
@@ -388,7 +394,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
@@ -420,9 +426,17 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>2</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B5" t="s">
         <v>5</v>
       </c>
     </row>

--- a/config_Kim.xlsx
+++ b/config_Kim.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10911"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://smu-my.sharepoint.com/personal/keithtan_2022_accountancy_smu_edu_sg/Documents/Desktop/smu/subject/y4s2/capstone/ETL/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kimbogyeong/Documents/GitHub/ETL/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="33" documentId="11_AD4DB114E441178AC67DF4960696DC8E693EDF12" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8239CBB6-9DBA-4364-B786-E6359BDA72CC}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA224F6A-00F1-4541-993E-FBB14199F8F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="paths" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
   <si>
     <t>raw_data</t>
   </si>
@@ -37,15 +37,6 @@
     <t>schemas</t>
   </si>
   <si>
-    <t>C:\Users\user\OneDrive - Singapore Management University\Desktop\smu\subject\y4s2\capstone\raw data\raw data</t>
-  </si>
-  <si>
-    <t>C:\Users\user\OneDrive - Singapore Management University\Desktop\smu\subject\y4s2\capstone\cleaned data</t>
-  </si>
-  <si>
-    <t>C:\Users\user\OneDrive - Singapore Management University\Desktop\smu\subject\y4s2\capstone\schemas.xlsx</t>
-  </si>
-  <si>
     <t>Setting</t>
   </si>
   <si>
@@ -73,10 +64,25 @@
     <t>tenant_turnover</t>
   </si>
   <si>
-    <t>C:\Users\user\OneDrive - Singapore Management University\Desktop\smu\subject\y4s2\capstone\combined data</t>
-  </si>
-  <si>
     <t>combined_data</t>
+  </si>
+  <si>
+    <t>/Users/kimbogyeong/Desktop/Capstone/raw data</t>
+  </si>
+  <si>
+    <t>/Users/kimbogyeong/Desktop/Capstone/Cleaned data</t>
+  </si>
+  <si>
+    <t>/Users/kimbogyeong/Desktop/Capstone/Combined data</t>
+  </si>
+  <si>
+    <t>/Users/kimbogyeong/Desktop/Capstone/schemas.xlsx</t>
+  </si>
+  <si>
+    <t>shop_mapping</t>
+  </si>
+  <si>
+    <t>/Users/kimbogyeong/Desktop/Capstone/shop_mapping.xlsx</t>
   </si>
 </sst>
 </file>
@@ -394,50 +400,58 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -448,52 +462,52 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9EF9E44-D244-4891-A14F-02851A432852}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15.140625" customWidth="1"/>
+    <col min="1" max="1" width="15.1640625" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" customWidth="1"/>
+    <col min="3" max="3" width="15.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>8</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B2" t="s">
         <v>9</v>
-      </c>
-      <c r="C1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" t="s">
-        <v>12</v>
       </c>
       <c r="C2">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C3">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
         <v>11</v>
-      </c>
-      <c r="B4" t="s">
-        <v>14</v>
       </c>
       <c r="C4">
         <v>7</v>

--- a/config_Kim.xlsx
+++ b/config_Kim.xlsx
@@ -450,7 +450,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>C:\Users\user\OneDrive - Singapore Management University\Desktop\smu\subject\y4s2\capstone\raw data\raw data</t>
+          <t>/Users/kimbogyeong/Desktop/Capstone/raw data</t>
         </is>
       </c>
     </row>
@@ -462,7 +462,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>C:\Users\user\OneDrive - Singapore Management University\Desktop\smu\subject\y4s2\capstone\cleaned data</t>
+          <t>/Users/kimbogyeong/Desktop/Capstone/Cleaned data</t>
         </is>
       </c>
     </row>
@@ -474,7 +474,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>C:\Users\user\OneDrive - Singapore Management University\Desktop\smu\subject\y4s2\capstone\combined data</t>
+          <t>/Users/kimbogyeong/Desktop/Capstone/Combined data</t>
         </is>
       </c>
     </row>
@@ -486,7 +486,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>C:\Users\user\OneDrive - Singapore Management University\Desktop\smu\subject\y4s2\capstone\schemas.xlsx</t>
+          <t>/Users/kimbogyeong/Desktop/Capstone/schemas.xlsx</t>
         </is>
       </c>
     </row>
@@ -498,7 +498,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>C:\Users\user\OneDrive - Singapore Management University\Desktop\smu\subject\y4s2\capstone\shop_mapping.xlsx</t>
+          <t>/Users/kimbogyeong/Desktop/Capstone/shop_mapping.xlsx</t>
         </is>
       </c>
     </row>
@@ -636,7 +636,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>winsorise</t>
+          <t>none</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>cap</t>
+          <t>drop_row</t>
         </is>
       </c>
     </row>

--- a/config_Kim.xlsx
+++ b/config_Kim.xlsx
@@ -1,39 +1,135 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10911"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kimbogyeong/Documents/GitHub/ETL/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{061A60F0-C09A-FE46-B9A0-92E2E2081E00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="1900" yWindow="1440" windowWidth="18560" windowHeight="9040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="paths" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="gto_headers" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="data_cleaning" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="paths" sheetId="1" r:id="rId1"/>
+    <sheet name="gto_headers" sheetId="2" r:id="rId2"/>
+    <sheet name="data_cleaning" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="28">
+  <si>
+    <t>Setting</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>raw_data</t>
+  </si>
+  <si>
+    <t>cleaned_data</t>
+  </si>
+  <si>
+    <t>combined_data</t>
+  </si>
+  <si>
+    <t>schemas</t>
+  </si>
+  <si>
+    <t>/Users/kimbogyeong/Desktop/Capstone/schemas.xlsx</t>
+  </si>
+  <si>
+    <t>shop_mapping</t>
+  </si>
+  <si>
+    <t>/Users/kimbogyeong/Desktop/Capstone/shop_mapping.xlsx</t>
+  </si>
+  <si>
+    <t>category</t>
+  </si>
+  <si>
+    <t>dataset</t>
+  </si>
+  <si>
+    <t>header_row</t>
+  </si>
+  <si>
+    <t>gto</t>
+  </si>
+  <si>
+    <t>monthly_sales</t>
+  </si>
+  <si>
+    <t>monthly_rent</t>
+  </si>
+  <si>
+    <t>tenant_turnover</t>
+  </si>
+  <si>
+    <t>blank_numeric</t>
+  </si>
+  <si>
+    <t>zero</t>
+  </si>
+  <si>
+    <t>blank_string</t>
+  </si>
+  <si>
+    <t>empty</t>
+  </si>
+  <si>
+    <t>outlier_method</t>
+  </si>
+  <si>
+    <t>none</t>
+  </si>
+  <si>
+    <t>outlier_action</t>
+  </si>
+  <si>
+    <t>drop_row</t>
+  </si>
+  <si>
+    <t>outlier_threshold</t>
+  </si>
+  <si>
+    <t>/Users/kimbogyeong/Desktop/Capstone1/raw_data</t>
+  </si>
+  <si>
+    <t>/Users/kimbogyeong/Desktop/Capstone1/cleaned_data</t>
+  </si>
+  <si>
+    <t>/Users/kimbogyeong/Desktop/Capstone1/combined_data</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -48,93 +144,43 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -422,84 +468,56 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>raw_data</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>/Users/kimbogyeong/Desktop/Capstone/raw data</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>cleaned_data</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>/Users/kimbogyeong/Desktop/Capstone/Cleaned data</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>combined_data</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>/Users/kimbogyeong/Desktop/Capstone/Combined data</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>schemas</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>/Users/kimbogyeong/Desktop/Capstone/schemas.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>shop_mapping</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>/Users/kimbogyeong/Desktop/Capstone/shop_mapping.xlsx</t>
-        </is>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -508,73 +526,51 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>dataset</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>header_row</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>gto</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>monthly_sales</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2">
         <v>7</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>gto</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>monthly_rent</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3">
         <v>8</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>gto</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>tenant_turnover</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4">
         <v>7</v>
       </c>
     </row>
@@ -584,81 +580,55 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>blank_numeric</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>zero</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>blank_string</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>empty</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>outlier_method</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>outlier_action</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>drop_row</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>outlier_threshold</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6">
         <v>5</v>
       </c>
     </row>
